--- a/光伏配储项目/电价数据/2026/榕江站.xlsx
+++ b/光伏配储项目/电价数据/2026/榕江站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.34792</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.84733</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.40314</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26713</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.08034000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.61021</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17819</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.27919</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25942</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24872</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.37303</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.66555</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.42417</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.43692</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.60873</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.59113</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.75905</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.18942</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39995</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.62395</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43941</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44689</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.68024</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.93389</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.53522</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.25544</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.39243</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.13974</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.17237</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.36694</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.48154</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.48179</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7436900000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7992100000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.2605</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.02575</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.93671</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.82605</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.78898</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5315</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.50126</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.48266</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42738</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4383</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7513</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.93245</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.00807</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5406</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.53128</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5314099999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.51183</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41274</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.49144</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3879</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38381</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.26616</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.23608</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.27456</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.39589</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.47951</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.38439</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.50987</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.5162100000000001</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.6999500000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6658500000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.8825299999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.36279</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.40142</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.7712</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5424099999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.6926100000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.4152</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.9866699999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62925</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.81262</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8750599999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.2409</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.67997</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.18834</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.90873</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.28286</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.17148</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.3536</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.09202</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.15608</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6980599999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.04497</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9468799999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.03636</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.9124099999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.14293</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.9474199999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45957</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.90191</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.94778</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45828</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43579</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4524</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33597</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5311</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5081600000000001</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5132599999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.46257</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39321</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.44516</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.46336</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40894</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.49558</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45558</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.45482</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.4045299999999999</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.13091</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.17025</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27021</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.08842</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.9202899999999999</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.7373200000000001</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.7228300000000001</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.92499</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.91887</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.90419</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.90515</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.1734</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.8788400000000001</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.87317</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.0377</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.55869</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.6243200000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.83139</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.84073</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.70741</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.7544299999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.53755</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.88993</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.46273</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39692</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45614</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51773</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.52728</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.60445</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.65259</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.65915</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.66753</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.36579</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.63761</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.69686</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4741</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5098199999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.65228</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.8110700000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7922</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.93553</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.47175</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.66525</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45749</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5427000000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6417</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.83226</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.59154</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.96309</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.7660800000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.63125</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.58035</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.71988</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46522</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34356</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5403300000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.51888</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.45673</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42363</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44412</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.43863</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.50988</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.65783</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.46198</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4576</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.28721</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.27863</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.70443</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.42921</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.65366</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.55941</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.46494</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.44571</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.51612</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.69937</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.49512</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.54115</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.48064</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40557</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.50497</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.6041</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.71388</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.5204500000000001</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.65598</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5571799999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.5275700000000001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50271</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.47599</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.4362799999999999</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.43136</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.34173</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14228</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.39199</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.4268</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.27753</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.26387</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.25032</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.11694</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.39468</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.08248</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26339</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30034</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.45342</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41972</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31384</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.22029</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.22956</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.22781</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28068</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.17733</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.15301</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.23805</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.17055</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24003</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.20281</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.17971</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.15929</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24017</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26261</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.18707</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09887</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04119</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009650000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2055</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04891</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19997</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.50414</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00605</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05965</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05785</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3138</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.38177</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.42794</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43735</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.47184</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78683</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87021</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.64659</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.56951</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20697</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.46001</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42379</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39468</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44296</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.44811</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5685</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.61314</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.92436</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.48874</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.27661</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.6117899999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8702000000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.3732200000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.6291100000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.47422</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.16578</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.25762</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.25672</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27225</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.25527</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27666</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.28889</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.29682</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32053</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9002899999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.28789</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29355</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30307</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.54057</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.41316</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.40692</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.45501</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.51954</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.21938</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.43076</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.22998</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4741</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.47158</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.31226</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.24571</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.93523</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.73065</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.31182</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7778200000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.9195399999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.72549</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.22847</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.23366</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.49654</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.55772</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.5142899999999999</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.42394</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.46202</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43064</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45642</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.47173</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.28202</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.44034</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.42146</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.28772</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40348</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.28308</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49149</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.17044</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29865</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.42334</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.27249</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15969</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.28567</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28551</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.00612</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.28763</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.2844100000000001</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.29818</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.46185</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.59874</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.29245</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.27551</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.27563</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.26564</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.26187</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.18584</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.1729</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.17926</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.1703</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.14689</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.2419</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.26206</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.15833</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.15657</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.19896</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.16677</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.20953</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.19412</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.17421</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.25427</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.2780899999999999</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.15248</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.29096</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.39652</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.15278</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.21463</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.41915</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.44205</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26696</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27791</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.28614</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.27755</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28376</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.28729</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.27108</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.28545</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.28285</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.28663</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.29034</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.28665</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.28765</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.41377</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.27675</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.27928</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.23928</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27448</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28444</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.29947</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.28627</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28594</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29128</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28066</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28371</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28878</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28459</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28749</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.48204</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29608</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28241</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.27823</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.27807</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.29967</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.2758</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.27878</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.28682</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29228</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29397</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.28824</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.28849</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30204</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.28933</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.28995</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.2794700000000001</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.192</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.42436</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.7055800000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.39176</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.50904</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48081</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5168200000000001</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.44046</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.57939</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27522</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.4191</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25143</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.74272</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.47787</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.40203</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.44219</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40496</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.5653899999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.42653</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.41838</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.45664</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.44577</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.45253</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.68332</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.47629</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.43201</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.48974</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.45456</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7207100000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.23725</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.48064</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.23188</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.27082</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.27763</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.19932</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.2728</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27247</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.26976</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.18273</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.26856</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.2699</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.26863</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.26827</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.17724</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29203</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.17474</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.13502</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.22594</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.2868</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.25523</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.17447</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.18031</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.21617</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.18615</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.1468</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.13898</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.20287</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.22858</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27484</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28548</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.29168</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.25187</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.29141</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.28461</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.27216</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.23399</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.24015</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28037</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.26133</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.27932</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.26413</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.27489</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.27865</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.22059</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.26715</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.20977</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.15759</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.22188</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3166</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.28735</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27324</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28258</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.26675</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.27969</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.27375</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.27693</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.27642</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.26576</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.27851</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28321</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28266</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27388</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.27699</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.28765</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.2677</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.27898</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26626</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40562</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6328400000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.51193</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.18604</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29149</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40982</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37216</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44038</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.4852</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6655</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.66908</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.30304</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.82541</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.50501</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.41362</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.45052</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.30925</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.27481</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.2832</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.26333</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.28022</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.26621</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4432</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41332</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.45345</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.49112</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.53196</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.56687</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.42338</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6770700000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.83114</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39281</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.5600499999999999</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.43499</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.29845</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.29914</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.28085</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.26195</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.27295</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.74919</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5980800000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.63922</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.29888</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38289</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.24522</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.27457</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.04474</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.26503</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.27531</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.26346</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.27098</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28309</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.40637</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.44313</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40901</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42457</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42931</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.41648</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.41333</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.22143</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41863</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.22438</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.21978</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.2443</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.27763</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.26954</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.23192</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.27017</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.28193</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.17213</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.18585</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.17821</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.21388</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.17837</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.26893</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.26168</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.2163</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.26176</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.2039</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.04585</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.2521</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.04694</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.04601</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.14677</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.18384</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.14553</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.04505</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.1371</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.14117</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.17994</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.13906</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.14152</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.14397</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.04467</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.14643</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.04469</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.15628</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.16677</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.1303</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27219</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.41414</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.26961</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.6495700000000001</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00421</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.40658</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28367</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28209</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.23758</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.26384</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.25772</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.2685</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.26342</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.20209</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.23563</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.21687</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.23038</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.26301</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.28909</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.24709</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.24243</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.16041</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.16706</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.24707</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.15078</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.27356</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.15388</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.23219</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.21844</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.27668</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.27297</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.26546</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.00825</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.16897</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.16622</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.2605</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.18916</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21208</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.20309</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.00215</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.18366</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.15964</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.03892</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24102</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.00021</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.01027</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.16023</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02211</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01366</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04299</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04090999999999999</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.0432</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00376</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03543</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.008199999999999999</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03506</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20962</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27058</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29085</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27659</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.29097</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28629</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.2596</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.27812</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.27693</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.26094</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.26344</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26666</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.14621</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.14245</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.14647</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.14412</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.14052</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.13055</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41142</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.16833</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26658</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.21582</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.23413</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8545499999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8630399999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.0861</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.04675</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24073</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28594</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.62652</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00286</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00206</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47575</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.6138899999999999</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.51397</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.7735</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9741000000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.60454</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8294600000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.82769</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.83208</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93257</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.2994</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.47159</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.27403</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.25239</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.24814</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.16631</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.24801</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.24145</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.23541</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.19962</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.22659</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.18432</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.14489</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.18021</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.13995</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.14239</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.13025</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.15817</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.21197</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.25787</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.22525</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.23348</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.24374</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.26855</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.29026</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.27495</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25875</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39478</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28286</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28421</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.28854</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5887100000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.44029</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.46794</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.42827</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.48304</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8484700000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.84484</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.40507</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5519500000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.69204</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8965</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.57787</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.41979</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19552</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31094</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.39754</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.28604</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36435</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.53507</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.54332</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.17346</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.86637</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.57629</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.75734</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.4935</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.60472</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.53607</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.44095</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.73133</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.67549</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.12055</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.87164</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.7450800000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.60517</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31558</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.28876</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28256</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28217</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.27641</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28198</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.2611</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42133</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.52961</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.1978</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43464</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39083</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.43671</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.48788</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.43173</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5307000000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42834</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.45096</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40565</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47302</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.58199</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4921</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.41832</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.43079</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.31913</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.72605</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.46415</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43192</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.41934</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.26251</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.44575</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.45853</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.44748</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.46846</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.43627</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.5305800000000001</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.42824</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.42003</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39765</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33388</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17617</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14583</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19875</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14747</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04844</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.1221</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26013</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14268</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14597</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18678</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22695</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27493</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.17083</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20419</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.16771</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.43804</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.55461</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.41086</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.42357</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.44947</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40528</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.48941</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.4348399999999999</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.41794</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.46739</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.45385</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4731</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40629</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39289</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36554</v>
       </c>
     </row>
   </sheetData>
